--- a/AAII_Financials/Yearly/TUSK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TUSK_YR_FIN.xlsx
@@ -1357,7 +1357,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="3">
-        <v>4000</v>
+        <v>4700</v>
       </c>
       <c r="F22" s="3">
         <v>16200</v>
